--- a/by_venue/T-FR.xlsx
+++ b/by_venue/T-FR.xlsx
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4288,7 +4288,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
